--- a/Impact modelling/Correlations_water_municipalities_months.xlsx
+++ b/Impact modelling/Correlations_water_municipalities_months.xlsx
@@ -438,10 +438,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.6388907857687365</v>
+        <v>0.6369684110640301</v>
       </c>
       <c r="C2">
-        <v>13.52332855461029</v>
+        <v>13.51135184981918</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -453,7 +453,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>0.8021646686960819</v>
+        <v>0.8007198033104566</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -464,10 +464,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.5072786397567033</v>
+        <v>0.4976586588706806</v>
       </c>
       <c r="C3">
-        <v>14.71977285186196</v>
+        <v>15.17825522029407</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -479,10 +479,10 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>0.7130510394293815</v>
+        <v>0.7060824608608223</v>
       </c>
       <c r="H3">
-        <v>4.750669021742132E-110</v>
+        <v>1.11519717115551E-82</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -490,10 +490,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.5781301149500684</v>
+        <v>0.5730943422334642</v>
       </c>
       <c r="C4">
-        <v>14.76918202138385</v>
+        <v>14.78772147940452</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -505,10 +505,10 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>0.7653100323933342</v>
+        <v>0.7616885698778373</v>
       </c>
       <c r="H4">
-        <v>4.056225232671723E-298</v>
+        <v>2.418459885746784E-239</v>
       </c>
     </row>
   </sheetData>

--- a/Impact modelling/Correlations_water_municipalities_months.xlsx
+++ b/Impact modelling/Correlations_water_municipalities_months.xlsx
@@ -438,10 +438,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.6369684110640301</v>
+        <v>0.6189606284066183</v>
       </c>
       <c r="C2">
-        <v>13.51135184981918</v>
+        <v>13.65907203865699</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -453,7 +453,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>0.8007198033104566</v>
+        <v>0.7943040991298788</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -464,10 +464,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.4976586588706806</v>
+        <v>0.3932433663103303</v>
       </c>
       <c r="C3">
-        <v>15.17825522029407</v>
+        <v>16.79158745003904</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -479,10 +479,10 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>0.7060824608608223</v>
+        <v>0.6276697866261353</v>
       </c>
       <c r="H3">
-        <v>1.11519717115551E-82</v>
+        <v>2.45826500927732E-121</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -490,10 +490,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.5730943422334642</v>
+        <v>0.5559483457680063</v>
       </c>
       <c r="C4">
-        <v>14.78772147940452</v>
+        <v>14.73273375501254</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -505,10 +505,10 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>0.7616885698778373</v>
+        <v>0.7527841920482529</v>
       </c>
       <c r="H4">
-        <v>2.418459885746784E-239</v>
+        <v>4.639343350807395E-247</v>
       </c>
     </row>
   </sheetData>
